--- a/data/sample/示例数据/附件1：中药上市公司基本信息（截至到2025年12月22日）.xlsx
+++ b/data/sample/示例数据/附件1：中药上市公司基本信息（截至到2025年12月22日）.xlsx
@@ -11,7 +11,7 @@
     <sheet name="字段说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">基本信息表!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">基本信息表!$A$1:$L$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="357">
   <si>
     <t>序号</t>
   </si>
@@ -69,6 +69,51 @@
     <t>管理人员人数</t>
   </si>
   <si>
+    <t>白云山</t>
+  </si>
+  <si>
+    <t>广州白云山医药集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Guangzhou Baiyunshan Pharmaceutical Holdings Company Limited</t>
+  </si>
+  <si>
+    <t>制造业-医药制造业</t>
+  </si>
+  <si>
+    <t>上海证券交易所</t>
+  </si>
+  <si>
+    <t>上交所主板A股</t>
+  </si>
+  <si>
+    <t>广东省广州市</t>
+  </si>
+  <si>
+    <t>16.26亿</t>
+  </si>
+  <si>
+    <t>云南白药</t>
+  </si>
+  <si>
+    <t>云南白药集团股份有限公司</t>
+  </si>
+  <si>
+    <t>YUNNAN BAIYAO GROUP CO.,LTD</t>
+  </si>
+  <si>
+    <t>深圳证券交易所</t>
+  </si>
+  <si>
+    <t>深交所主板A股</t>
+  </si>
+  <si>
+    <t>云南省昆明市</t>
+  </si>
+  <si>
+    <t>17.84亿</t>
+  </si>
+  <si>
     <t>华润三九</t>
   </si>
   <si>
@@ -78,21 +123,492 @@
     <t>China Resources Sanjiu Medical &amp; Pharmaceutical Co., Ltd.</t>
   </si>
   <si>
-    <t>制造业-医药制造业</t>
-  </si>
-  <si>
-    <t>深圳证券交易所</t>
-  </si>
-  <si>
-    <t>深交所主板A股</t>
-  </si>
-  <si>
     <t>广东省深圳市</t>
   </si>
   <si>
     <t>16.64亿</t>
   </si>
   <si>
+    <t>同仁堂</t>
+  </si>
+  <si>
+    <t>北京同仁堂股份有限公司</t>
+  </si>
+  <si>
+    <t>BEIJING TONG REN TANG CO., LTD</t>
+  </si>
+  <si>
+    <t>北京市</t>
+  </si>
+  <si>
+    <t>13.71亿</t>
+  </si>
+  <si>
+    <t>太极集团</t>
+  </si>
+  <si>
+    <t>重庆太极实业(集团)股份有限公司</t>
+  </si>
+  <si>
+    <t>Chongqing Taiji Industry (Group) Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>重庆市</t>
+  </si>
+  <si>
+    <t>5.514亿</t>
+  </si>
+  <si>
+    <t>步长制药</t>
+  </si>
+  <si>
+    <t>山东步长制药股份有限公司</t>
+  </si>
+  <si>
+    <t>SHANDONG BUCHANG PHARMACEUTICALS CO., LTD.</t>
+  </si>
+  <si>
+    <t>山东省菏泽市</t>
+  </si>
+  <si>
+    <t>10.55亿</t>
+  </si>
+  <si>
+    <t>以岭药业</t>
+  </si>
+  <si>
+    <t>石家庄以岭药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Shijiazhuang Yiling Pharmaceutical Co., Ltd.</t>
+  </si>
+  <si>
+    <t>河北省石家庄市</t>
+  </si>
+  <si>
+    <t>16.71亿</t>
+  </si>
+  <si>
+    <t>片仔癀</t>
+  </si>
+  <si>
+    <t>漳州片仔癀药业股份有限公司</t>
+  </si>
+  <si>
+    <t>ZHANGZHOU PIENTZEHUANG PHARMACEUTICAL CO., LTD.</t>
+  </si>
+  <si>
+    <t>福建省漳州市</t>
+  </si>
+  <si>
+    <t>6.033亿</t>
+  </si>
+  <si>
+    <t>济川药业</t>
+  </si>
+  <si>
+    <t>湖北济川药业股份有限公司</t>
+  </si>
+  <si>
+    <t>HUBEI JUMPCAN PHARMACEUTICAL CO., LTD.</t>
+  </si>
+  <si>
+    <t>湖北省荆州市</t>
+  </si>
+  <si>
+    <t>9.212亿</t>
+  </si>
+  <si>
+    <t>天士力</t>
+  </si>
+  <si>
+    <t>天士力医药集团股份有限公司</t>
+  </si>
+  <si>
+    <t>TASLY PHARMACEUTICAL GROUP CO.,LTD.</t>
+  </si>
+  <si>
+    <t>天津市</t>
+  </si>
+  <si>
+    <t>14.94亿</t>
+  </si>
+  <si>
+    <t>达仁堂</t>
+  </si>
+  <si>
+    <t>津药达仁堂集团股份有限公司</t>
+  </si>
+  <si>
+    <t>TIANJIN PHARMACEUTICAL DA REN TANG GROUP CORPORATION LIMITED</t>
+  </si>
+  <si>
+    <t>7.701亿</t>
+  </si>
+  <si>
+    <t>瑞康医药</t>
+  </si>
+  <si>
+    <t>瑞康医药集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Realcan Pharmaceutical Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>山东省烟台市</t>
+  </si>
+  <si>
+    <t>15.05亿</t>
+  </si>
+  <si>
+    <t>昆药集团</t>
+  </si>
+  <si>
+    <t>昆药集团股份有限公司</t>
+  </si>
+  <si>
+    <t>KPC Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>7.570亿</t>
+  </si>
+  <si>
+    <t>康恩贝</t>
+  </si>
+  <si>
+    <t>浙江康恩贝制药股份有限公司</t>
+  </si>
+  <si>
+    <t>ZhejiangCONBAPharmaceuticalCo.,Ltd.</t>
+  </si>
+  <si>
+    <t>浙江省兰溪市</t>
+  </si>
+  <si>
+    <t>25.34亿</t>
+  </si>
+  <si>
+    <t>信邦制药</t>
+  </si>
+  <si>
+    <t>贵州信邦制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Guizhou Xinbang Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>批发和零售业</t>
+  </si>
+  <si>
+    <t>贵州省黔南布依族苗族自治州</t>
+  </si>
+  <si>
+    <t>19.44亿</t>
+  </si>
+  <si>
+    <t>红日药业</t>
+  </si>
+  <si>
+    <t>天津红日药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Tianjin Chase Sun Pharmaceutical Co.,Ltd</t>
+  </si>
+  <si>
+    <t>深交所创业板A股</t>
+  </si>
+  <si>
+    <t>30.04亿</t>
+  </si>
+  <si>
+    <t>葵花药业</t>
+  </si>
+  <si>
+    <t>葵花药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Sunflower Pharmaceutical Group Co.,Ltd</t>
+  </si>
+  <si>
+    <t>黑龙江省哈尔滨</t>
+  </si>
+  <si>
+    <t>5.840亿</t>
+  </si>
+  <si>
+    <t>仁和药业</t>
+  </si>
+  <si>
+    <t>仁和药业股份有限公司</t>
+  </si>
+  <si>
+    <t>RENHE PHARMACY CO.,LTD</t>
+  </si>
+  <si>
+    <t>江西省宜春市</t>
+  </si>
+  <si>
+    <t>14.00亿</t>
+  </si>
+  <si>
+    <t>康美药业</t>
+  </si>
+  <si>
+    <t>康美药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Kangmei Pharmaceutical Co.,Ltd</t>
+  </si>
+  <si>
+    <t>广东省普宁市</t>
+  </si>
+  <si>
+    <t>138.3亿</t>
+  </si>
+  <si>
+    <t>康缘药业</t>
+  </si>
+  <si>
+    <t>江苏康缘药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Jiangsu Kanion Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>江苏省连云港市</t>
+  </si>
+  <si>
+    <t>5.662亿</t>
+  </si>
+  <si>
+    <t>东阿阿胶</t>
+  </si>
+  <si>
+    <t>东阿阿胶股份有限公司</t>
+  </si>
+  <si>
+    <t>Dong-E-E-Jiao Co., Ltd.</t>
+  </si>
+  <si>
+    <t>山东省东阿县</t>
+  </si>
+  <si>
+    <t>6.44亿</t>
+  </si>
+  <si>
+    <t>江中药业</t>
+  </si>
+  <si>
+    <t>江中药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Jiangzhong Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>江西省南昌市</t>
+  </si>
+  <si>
+    <t>6.350亿</t>
+  </si>
+  <si>
+    <t>健民集团</t>
+  </si>
+  <si>
+    <t>健民药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Jianmin Pharmaceutical Group Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>批发和零售业-批发业</t>
+  </si>
+  <si>
+    <t>湖北省武汉市</t>
+  </si>
+  <si>
+    <t>1.534亿</t>
+  </si>
+  <si>
+    <t>康弘药业</t>
+  </si>
+  <si>
+    <t>成都康弘药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Chengdu Kanghong Pharmaceutical Group Co., Ltd</t>
+  </si>
+  <si>
+    <t>四川省成都市</t>
+  </si>
+  <si>
+    <t>9.213亿</t>
+  </si>
+  <si>
+    <t>千金药业</t>
+  </si>
+  <si>
+    <t>株洲千金药业股份有限公司</t>
+  </si>
+  <si>
+    <t>ZhuZhou QianJin Pharmaceutical Co.,Ltd</t>
+  </si>
+  <si>
+    <t>湖南省株洲市</t>
+  </si>
+  <si>
+    <t>4.922亿</t>
+  </si>
+  <si>
+    <t>振东制药</t>
+  </si>
+  <si>
+    <t>山西振东制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Shanxi Zhendong Pharmaceutical Co.,Ltd</t>
+  </si>
+  <si>
+    <t>山西省长治市</t>
+  </si>
+  <si>
+    <t>9.923亿</t>
+  </si>
+  <si>
+    <t>羚锐制药</t>
+  </si>
+  <si>
+    <t>河南羚锐制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Henan Lingrui Pharmaceutical Co.,Ltd</t>
+  </si>
+  <si>
+    <t>河南省新县</t>
+  </si>
+  <si>
+    <t>5.671亿</t>
+  </si>
+  <si>
+    <t>新里程</t>
+  </si>
+  <si>
+    <t>新里程健康科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>New Journey Health Technology Group Co.,LTD</t>
+  </si>
+  <si>
+    <t>卫生和社会工作-卫生</t>
+  </si>
+  <si>
+    <t>甘肃省陇南市</t>
+  </si>
+  <si>
+    <t>33.87亿</t>
+  </si>
+  <si>
+    <t>珍宝岛</t>
+  </si>
+  <si>
+    <t>黑龙江珍宝岛药业股份有限公司</t>
+  </si>
+  <si>
+    <t>HeiLongJiangZBDPharmaceuticalCo.,Ltd.</t>
+  </si>
+  <si>
+    <t>黑龙江省鸡西市</t>
+  </si>
+  <si>
+    <t>9.410亿</t>
+  </si>
+  <si>
+    <t>中恒集团</t>
+  </si>
+  <si>
+    <t>广西梧州中恒集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Guangxi Wuzhou Zhongheng Group Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>广西梧州市</t>
+  </si>
+  <si>
+    <t>31.84亿</t>
+  </si>
+  <si>
+    <t>马应龙</t>
+  </si>
+  <si>
+    <t>马应龙药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Mayinglong Pharmaceutical Group Co.,Ltd</t>
+  </si>
+  <si>
+    <t>4.311亿</t>
+  </si>
+  <si>
+    <t>亚宝药业</t>
+  </si>
+  <si>
+    <t>亚宝药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Yabao Pharmaceutical Group Co.Ltd.</t>
+  </si>
+  <si>
+    <t>山西省芮城县</t>
+  </si>
+  <si>
+    <t>6.920亿</t>
+  </si>
+  <si>
+    <t>九芝堂</t>
+  </si>
+  <si>
+    <t>九芝堂股份有限公司</t>
+  </si>
+  <si>
+    <t>Jiuzhitang Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>湖南省长沙市</t>
+  </si>
+  <si>
+    <t>8.559亿</t>
+  </si>
+  <si>
+    <t>益佰制药</t>
+  </si>
+  <si>
+    <t>贵州益佰制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Guizhou Yibai Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>贵州省贵阳市</t>
+  </si>
+  <si>
+    <t>7.919亿</t>
+  </si>
+  <si>
+    <t>众生药业</t>
+  </si>
+  <si>
+    <t>广东众生药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Guangdong Zhongsheng Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>广东省东莞市</t>
+  </si>
+  <si>
+    <t>8.499亿</t>
+  </si>
+  <si>
     <t>金花股份</t>
   </si>
   <si>
@@ -102,16 +618,448 @@
     <t>Ginwa Enterprise (Group) Inc.</t>
   </si>
   <si>
-    <t>上海证券交易所</t>
-  </si>
-  <si>
-    <t>上交所主板A股</t>
-  </si>
-  <si>
     <t>陕西省西安市</t>
   </si>
   <si>
     <t>3.733亿</t>
+  </si>
+  <si>
+    <t>神奇制药</t>
+  </si>
+  <si>
+    <t>上海神奇制药投资管理股份有限公司</t>
+  </si>
+  <si>
+    <t>ShanghaiShenqiPharmaceuticalInvestmentManagementCo.,Ltd.</t>
+  </si>
+  <si>
+    <t>上海市</t>
+  </si>
+  <si>
+    <t>5.341亿</t>
+  </si>
+  <si>
+    <t>桂林三金</t>
+  </si>
+  <si>
+    <t>桂林三金药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Guilin Sanjin Pharmaceutical Co., Ltd.</t>
+  </si>
+  <si>
+    <t>广西壮族自治区桂林市</t>
+  </si>
+  <si>
+    <t>5.876亿</t>
+  </si>
+  <si>
+    <t>太龙药业</t>
+  </si>
+  <si>
+    <t>河南太龙药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Henan Taloph Pharmaceutical Stock Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>河南省郑州市</t>
+  </si>
+  <si>
+    <t>5.739亿</t>
+  </si>
+  <si>
+    <t>奇正藏药</t>
+  </si>
+  <si>
+    <t>西藏奇正藏药股份有限公司</t>
+  </si>
+  <si>
+    <t>Xizang Cheezheng Xizang Medicine Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>西藏林芝市</t>
+  </si>
+  <si>
+    <t>5.721亿</t>
+  </si>
+  <si>
+    <t>佐力药业</t>
+  </si>
+  <si>
+    <t>浙江佐力药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Zhejiang Jolly Pharmaceutical Co., LTD</t>
+  </si>
+  <si>
+    <t>浙江省德清县</t>
+  </si>
+  <si>
+    <t>7.014亿</t>
+  </si>
+  <si>
+    <t>精华制药</t>
+  </si>
+  <si>
+    <t>精华制药集团股份有限公司</t>
+  </si>
+  <si>
+    <t>JINGHUA PHARMACEUTICAL GROUP CO., LTD.</t>
+  </si>
+  <si>
+    <t>江苏省南通市</t>
+  </si>
+  <si>
+    <t>8.297亿</t>
+  </si>
+  <si>
+    <t>万邦德</t>
+  </si>
+  <si>
+    <t>万邦德医药控股集团股份有限公司</t>
+  </si>
+  <si>
+    <t>WANBANGDE PHARMACEUTICAL HOLDING GROUP CO.,LTD.</t>
+  </si>
+  <si>
+    <t>浙江省湖州市</t>
+  </si>
+  <si>
+    <t>6.117亿</t>
+  </si>
+  <si>
+    <t>通化金马</t>
+  </si>
+  <si>
+    <t>通化金马药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>TONGHUA GOLDEN-HORSE PHARMACEUTICAL INDUSTRY CO,LTD</t>
+  </si>
+  <si>
+    <t>吉林省通化市</t>
+  </si>
+  <si>
+    <t>9.665亿</t>
+  </si>
+  <si>
+    <t>康泰医学</t>
+  </si>
+  <si>
+    <t>康泰医学系统(秦皇岛)股份有限公司</t>
+  </si>
+  <si>
+    <t>CONTEC MEDICAL SYSTEMS CO. , LTD.</t>
+  </si>
+  <si>
+    <t>制造业-专用设备制造业</t>
+  </si>
+  <si>
+    <t>河北省秦皇岛市</t>
+  </si>
+  <si>
+    <t>4.018亿</t>
+  </si>
+  <si>
+    <t>盘龙药业</t>
+  </si>
+  <si>
+    <t>陕西盘龙药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>SHAANXI PANLONG PHARMACEUTICAL GROUP LIMITED BY SHARE LTD</t>
+  </si>
+  <si>
+    <t>陕西省商洛市</t>
+  </si>
+  <si>
+    <t>1.063亿</t>
+  </si>
+  <si>
+    <t>华神科技</t>
+  </si>
+  <si>
+    <t>成都华神科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Chengdu huasun technology group Inc., LTD.</t>
+  </si>
+  <si>
+    <t>6.237亿</t>
+  </si>
+  <si>
+    <t>新天药业</t>
+  </si>
+  <si>
+    <t>贵阳新天药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Guiyang Xintian Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>2.441亿</t>
+  </si>
+  <si>
+    <t>恩威医药</t>
+  </si>
+  <si>
+    <t>恩威医药股份有限公司</t>
+  </si>
+  <si>
+    <t>Enwei Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>西藏自治区昌都市</t>
+  </si>
+  <si>
+    <t>1.029亿</t>
+  </si>
+  <si>
+    <t>华森制药</t>
+  </si>
+  <si>
+    <t>重庆华森制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Chongqing Pharscin Pharmaceutical Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4.176亿</t>
+  </si>
+  <si>
+    <t>沃华医药</t>
+  </si>
+  <si>
+    <t>山东沃华医药科技股份有限公司</t>
+  </si>
+  <si>
+    <t>Shandong Wohua Pharmaceutical Co., Ltd.</t>
+  </si>
+  <si>
+    <t>山东省潍坊市</t>
+  </si>
+  <si>
+    <t>5.772亿</t>
+  </si>
+  <si>
+    <t>寿仙谷</t>
+  </si>
+  <si>
+    <t>浙江寿仙谷医药股份有限公司</t>
+  </si>
+  <si>
+    <t>Zhejiang Shouxiangu Pharmaceutical Co., Ltd.</t>
+  </si>
+  <si>
+    <t>浙江省武义县</t>
+  </si>
+  <si>
+    <t>1.982亿</t>
+  </si>
+  <si>
+    <t>特一药业</t>
+  </si>
+  <si>
+    <t>特一药业集团股份有限公司</t>
+  </si>
+  <si>
+    <t>TEYI PHARMACEUTICAL GROUP CO.,LTD</t>
+  </si>
+  <si>
+    <t>广东省台山市</t>
+  </si>
+  <si>
+    <t>5.130亿</t>
+  </si>
+  <si>
+    <t>益盛药业</t>
+  </si>
+  <si>
+    <t>吉林省集安益盛药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Jilin Jian Yisheng Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>吉林省集安市</t>
+  </si>
+  <si>
+    <t>3.310亿</t>
+  </si>
+  <si>
+    <t>康惠制药</t>
+  </si>
+  <si>
+    <t>陕西康惠制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Shaanxi Kanghui Pharmaceutical CO., LTD.</t>
+  </si>
+  <si>
+    <t>陕西省咸阳市</t>
+  </si>
+  <si>
+    <t>9988万</t>
+  </si>
+  <si>
+    <t>嘉应制药</t>
+  </si>
+  <si>
+    <t>广东嘉应制药股份有限公司</t>
+  </si>
+  <si>
+    <t>GUANGDONG JIAYING PHARMACEUTICAL CO.,LTD</t>
+  </si>
+  <si>
+    <t>广东省梅州市</t>
+  </si>
+  <si>
+    <t>5.075亿</t>
+  </si>
+  <si>
+    <t>维康药业</t>
+  </si>
+  <si>
+    <t>浙江维康药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Zhejiang Wecome Pharmaceutical Company Limited</t>
+  </si>
+  <si>
+    <t>浙江省丽水经济开发区</t>
+  </si>
+  <si>
+    <t>1.448亿</t>
+  </si>
+  <si>
+    <t>启迪药业</t>
+  </si>
+  <si>
+    <t>启迪药业集团股份公司</t>
+  </si>
+  <si>
+    <t>TUS-PHARMACEUTICAL GROUP CO., LTD.</t>
+  </si>
+  <si>
+    <t>湖南省衡阳市</t>
+  </si>
+  <si>
+    <t>2.395亿</t>
+  </si>
+  <si>
+    <t>粤万年青</t>
+  </si>
+  <si>
+    <t>广东万年青制药股份有限公司</t>
+  </si>
+  <si>
+    <t>GUANGDONG LIFESTRONG PHARMACY CO., LTD.</t>
+  </si>
+  <si>
+    <t>广东省汕头市</t>
+  </si>
+  <si>
+    <t>1.600亿</t>
+  </si>
+  <si>
+    <t>新光药业</t>
+  </si>
+  <si>
+    <t>浙江新光药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Zhejiang Xinguang Pharmaceutical Co., Ltd.</t>
+  </si>
+  <si>
+    <t>浙江省嵊州市</t>
+  </si>
+  <si>
+    <t>天目药业</t>
+  </si>
+  <si>
+    <t>杭州天目山药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Hangzhou TianMuShan Pharmaceutical Enterprise Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>浙江省杭州市</t>
+  </si>
+  <si>
+    <t>1.218亿</t>
+  </si>
+  <si>
+    <t>莱茵生物</t>
+  </si>
+  <si>
+    <t>桂林莱茵生物科技股份有限公司</t>
+  </si>
+  <si>
+    <t>Guilin Layn Natural Ingredients Corp.</t>
+  </si>
+  <si>
+    <t>广西壮族自治区桂林市临桂区</t>
+  </si>
+  <si>
+    <t>7.416亿</t>
+  </si>
+  <si>
+    <t>广誉远</t>
+  </si>
+  <si>
+    <t>广誉远中药股份有限公司</t>
+  </si>
+  <si>
+    <t>GuangYuYuan Chinese Herbal Medicine Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>山西省晋中市</t>
+  </si>
+  <si>
+    <t>4.895亿</t>
+  </si>
+  <si>
+    <t>贵州三力</t>
+  </si>
+  <si>
+    <t>贵州三力制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Guizhou Sanli Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>贵州省安顺市</t>
+  </si>
+  <si>
+    <t>4.089亿</t>
+  </si>
+  <si>
+    <t>方盛制药</t>
+  </si>
+  <si>
+    <t>湖南方盛制药股份有限公司</t>
+  </si>
+  <si>
+    <t>Hunan Fangsheng Pharmaceutical Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>4.391亿</t>
+  </si>
+  <si>
+    <t>陇神戎发</t>
+  </si>
+  <si>
+    <t>甘肃陇神戎发药业股份有限公司</t>
+  </si>
+  <si>
+    <t>Gansu Longshenrongfa Pharmaceutical Industry CO. ,LTD</t>
+  </si>
+  <si>
+    <t>甘肃省兰州市</t>
+  </si>
+  <si>
+    <t>3.033亿</t>
   </si>
   <si>
     <t>字段名称</t>
@@ -167,7 +1115,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,6 +1126,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF505050"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -520,12 +1474,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD7D7D7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD7D7D7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD7D7D7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD7D7D7"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -646,156 +1615,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1323,10 +2295,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="2"/>
+  <dimension ref="A1:L67"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1"/>
   <cols>
-    <col min="2" max="2" width="11.4594594594595" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.4594594594595" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.4324324324324" customWidth="1"/>
     <col min="4" max="4" width="34.3873873873874" customWidth="1"/>
     <col min="5" max="5" width="9.5045045045045" customWidth="1"/>
@@ -1339,117 +2311,2549 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="5">
+    <row r="2" spans="1:12">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
+        <v>600332</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="4">
+        <v>27425</v>
+      </c>
+      <c r="L2" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
+        <v>538</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="4">
+        <v>9277</v>
+      </c>
+      <c r="L3" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
         <v>999</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="4">
+        <v>20031</v>
+      </c>
+      <c r="L4" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
+        <v>600085</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="4">
+        <v>17883</v>
+      </c>
+      <c r="L5" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
+        <v>600129</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="4">
+        <v>11971</v>
+      </c>
+      <c r="L6" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>603858</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="4">
+        <v>7689</v>
+      </c>
+      <c r="L7" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2603</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="4">
+        <v>11708</v>
+      </c>
+      <c r="L8" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <v>600436</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="4">
+        <v>2839</v>
+      </c>
+      <c r="L9" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <v>600566</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="4">
+        <v>5026</v>
+      </c>
+      <c r="L10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="14.85" spans="1:12">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <v>600535</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="4">
+        <v>10958</v>
+      </c>
+      <c r="L11" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="14.85" spans="1:12">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <v>600329</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12" s="4">
+        <v>3835</v>
+      </c>
+      <c r="L12" s="4">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2589</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="4">
+        <v>2897</v>
+      </c>
+      <c r="L13" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="B14" s="5">
+        <v>600422</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="4">
+        <v>5275</v>
+      </c>
+      <c r="L14" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="B15" s="5">
+        <v>600572</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8258</v>
+      </c>
+      <c r="L15" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2390</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="4">
+        <v>5059</v>
+      </c>
+      <c r="L16" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
+        <v>300026</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K17" s="4">
+        <v>5297</v>
+      </c>
+      <c r="L17" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2737</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K18" s="4">
+        <v>5727</v>
+      </c>
+      <c r="L18" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="B19" s="5">
+        <v>650</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="4">
+        <v>5394</v>
+      </c>
+      <c r="L19" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="K2" s="5">
-        <v>20031</v>
-      </c>
-      <c r="L2" s="5">
+      <c r="B20" s="5">
+        <v>600518</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K20" s="4">
+        <v>4233</v>
+      </c>
+      <c r="L20" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5">
+        <v>600557</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K21" s="4">
+        <v>6132</v>
+      </c>
+      <c r="L21" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5">
+        <v>423</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K22" s="4">
+        <v>4095</v>
+      </c>
+      <c r="L22" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="B23" s="5">
+        <v>600750</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="K23" s="4">
+        <v>4182</v>
+      </c>
+      <c r="L23" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5">
+        <v>600976</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="K24" s="4">
+        <v>2345</v>
+      </c>
+      <c r="L24" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2773</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K25" s="4">
+        <v>4462</v>
+      </c>
+      <c r="L25" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5">
+        <v>600479</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K26" s="4">
+        <v>5270</v>
+      </c>
+      <c r="L26" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5">
+        <v>300158</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="4">
+        <v>3720</v>
+      </c>
+      <c r="L27" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5">
+        <v>600285</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K28" s="4">
+        <v>2435</v>
+      </c>
+      <c r="L28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2219</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="K29" s="4">
+        <v>9097</v>
+      </c>
+      <c r="L29" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5">
+        <v>603567</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K30" s="4">
+        <v>2349</v>
+      </c>
+      <c r="L30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5">
+        <v>600252</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="K31" s="4">
+        <v>2971</v>
+      </c>
+      <c r="L31" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5">
+        <v>600993</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="K32" s="4">
+        <v>2654</v>
+      </c>
+      <c r="L32" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5">
+        <v>600351</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="K33" s="4">
+        <v>3611</v>
+      </c>
+      <c r="L33" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5">
+        <v>989</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="K34" s="4">
+        <v>3689</v>
+      </c>
+      <c r="L34" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5">
+        <v>600594</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="K35" s="4">
+        <v>5261</v>
+      </c>
+      <c r="L35" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5">
+        <v>2317</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K36" s="4">
+        <v>1775</v>
+      </c>
+      <c r="L36" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5">
         <v>600080</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="C37" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K37" s="4">
+        <v>588</v>
+      </c>
+      <c r="L37" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5">
+        <v>600613</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K38" s="4">
+        <v>1266</v>
+      </c>
+      <c r="L38" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5">
+        <v>2275</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H39" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="5">
-        <v>588</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="I39" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="K39" s="4">
+        <v>2567</v>
+      </c>
+      <c r="L39" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5">
+        <v>600222</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K40" s="4">
+        <v>2214</v>
+      </c>
+      <c r="L40" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5">
+        <v>2287</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="K41" s="4">
+        <v>3170</v>
+      </c>
+      <c r="L41" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5">
+        <v>300181</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K42" s="4">
+        <v>2861</v>
+      </c>
+      <c r="L42" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5">
+        <v>2349</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="K43" s="4">
+        <v>1490</v>
+      </c>
+      <c r="L43" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2082</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K44" s="4">
+        <v>1499</v>
+      </c>
+      <c r="L44" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5">
+        <v>766</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K45" s="4">
+        <v>1532</v>
+      </c>
+      <c r="L45" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5">
+        <v>300869</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="K46" s="4">
+        <v>1611</v>
+      </c>
+      <c r="L46" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5">
+        <v>2864</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="K47" s="4">
+        <v>933</v>
+      </c>
+      <c r="L47" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5">
+        <v>790</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="K48" s="4">
+        <v>918</v>
+      </c>
+      <c r="L48" s="4">
         <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5">
+        <v>2873</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="K49" s="4">
+        <v>1682</v>
+      </c>
+      <c r="L49" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5">
+        <v>301331</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="K50" s="4">
+        <v>1548</v>
+      </c>
+      <c r="L50" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5">
+        <v>2907</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K51" s="4">
+        <v>1384</v>
+      </c>
+      <c r="L51" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5">
+        <v>2107</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K52" s="4">
+        <v>1089</v>
+      </c>
+      <c r="L52" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5">
+        <v>603896</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="K53" s="4">
+        <v>1118</v>
+      </c>
+      <c r="L53" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5">
+        <v>2728</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="K54" s="4">
+        <v>1341</v>
+      </c>
+      <c r="L54" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5">
+        <v>2566</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K55" s="4">
+        <v>1656</v>
+      </c>
+      <c r="L55" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5">
+        <v>603139</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="K56" s="4">
+        <v>906</v>
+      </c>
+      <c r="L56" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5">
+        <v>2198</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="K57" s="4">
+        <v>594</v>
+      </c>
+      <c r="L57" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5">
+        <v>300878</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K58" s="4">
+        <v>650</v>
+      </c>
+      <c r="L58" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5">
+        <v>590</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="K59" s="4">
+        <v>1159</v>
+      </c>
+      <c r="L59" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5">
+        <v>301111</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="K60" s="4">
+        <v>667</v>
+      </c>
+      <c r="L60" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5">
+        <v>300519</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="K61" s="4">
+        <v>316</v>
+      </c>
+      <c r="L61" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5">
+        <v>600671</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K62" s="4">
+        <v>362</v>
+      </c>
+      <c r="L62" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5">
+        <v>2166</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="K63" s="4">
+        <v>1347</v>
+      </c>
+      <c r="L63" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5">
+        <v>600771</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="K64" s="4">
+        <v>1735</v>
+      </c>
+      <c r="L64" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5">
+        <v>603439</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="K65" s="4">
+        <v>2852</v>
+      </c>
+      <c r="L65" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5">
+        <v>603998</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="K66" s="4">
+        <v>1807</v>
+      </c>
+      <c r="L66" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>300534</v>
+      </c>
+      <c r="C67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D67" t="s">
+        <v>339</v>
+      </c>
+      <c r="E67" t="s">
+        <v>340</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" t="s">
+        <v>94</v>
+      </c>
+      <c r="I67" t="s">
+        <v>341</v>
+      </c>
+      <c r="J67" t="s">
+        <v>342</v>
+      </c>
+      <c r="K67">
+        <v>634</v>
+      </c>
+      <c r="L67">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1466,10 +4870,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>343</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1477,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1485,7 +4889,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1493,7 +4897,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1501,7 +4905,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1509,7 +4913,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1517,7 +4921,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1525,7 +4929,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1533,7 +4937,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1541,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1549,7 +4953,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1557,7 +4961,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1565,7 +4969,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
